--- a/src/data/output/im_output.xlsx
+++ b/src/data/output/im_output.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -24,6 +24,11 @@
     <font>
       <name val="Calibri"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color rgb="FF2C3E50"/>
+      <sz val="12"/>
     </font>
     <font>
       <sz val="10"/>
@@ -49,12 +54,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -568,842 +576,2048 @@
           <t>25.00</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>22.11</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>784.11</t>
-        </is>
+      <c r="E3" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="F3" t="n">
+        <v>784.11</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>TS-002</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TS-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0095873</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>612.00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>12.74</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>649.74</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>TS-002</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TS-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0095888</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>900.00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>27.00</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>972.00</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>TS-003</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TS-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0095907</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>569.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>26.71</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>624.16</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>TS-004</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TS-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0095945</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>700.00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>32.99</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>757.99</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>TS-004</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TS-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0095898</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>15.75</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>540.75</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>TS-004</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TS-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0095894</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>626.00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>26.13</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>670.91</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>TS-005</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TS-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0095912</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>25.20</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>25.46</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>550.66</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>TS-006</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>TS-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0095896</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>808.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>33.32</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>866.32</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>TS-006</t>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TS-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0095901</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>18.38</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>518.38</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>TS-006</t>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TS-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0095946</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>31.50</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>556.50</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>TS-007</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TS-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0095904</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>919.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>45.95</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>989.95</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>TS-008</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TS-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0095893</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>535.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>16.80</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>576.80</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>TS-008</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TS-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0095900</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>11.81</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>536.99</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>TS-008</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TS-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0095967</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>760.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>22.80</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>807.80</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>TS-009</t>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TS-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0095902</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>10.50</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>535.50</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>TS-010</t>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TS-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0095952</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>560.00</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>TS-010</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TS-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0095905</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>852.00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>27.56</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>42.60</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>922.16</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>TS-010</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TS-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0095963</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>580.00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>27.53</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>632.53</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>TS-011</t>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TS-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0095906</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>791.00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>24.48</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>840.48</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>TS-012</t>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>TS-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0095887</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>25.90</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>540.90</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>TS-012</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TS-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0095908</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>513.00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>25.21</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>26.09</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>564.30</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TS-012</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>TS-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0095947</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>925.00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>38.00</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>988.00</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>TS-013</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>TS-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0095910</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>18.38</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>518.38</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>TS-014</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>TS-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0095891</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>700.00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>43.50</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>768.50</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>TS-014</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TS-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0095903</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>540.00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>27.00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>592.00</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>TS-014</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>TS-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0095909</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>15.75</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>540.75</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>TS-015</t>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TS-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0095914</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>11.81</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>536.99</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>TS-016</t>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>TS-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0095948</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>860.00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>25.80</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>910.80</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>TS-016</t>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TS-031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0095911</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>10.50</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>535.50</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>TS-016</t>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>TS-032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0095915</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>560.00</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>TS-017</t>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TS-033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0095918</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>758.00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>27.27</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>37.90</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>823.17</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>TS-018</t>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>TS-034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0095916</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>23.89</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>548.89</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>TS-018</t>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>TS-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0095917</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>646.00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>20.13</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>691.13</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>TS-018</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>TS-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0095965</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>25.90</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>540.90</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>TS-019</t>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TS-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0095920</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>25.20</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>25.46</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>550.66</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>TS-020</t>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>TS-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0095923</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>546.00</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>TS-020</t>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>TS-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0095921</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>879.00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>31.64</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>910.64</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>TS-020</t>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>TS-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0095964</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>31.50</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>556.50</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>TS-021</t>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>TS-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0095924</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>550.00</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>TS-022</t>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>TS-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0095951</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>15.75</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>540.75</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>TS-022</t>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>TS-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0095925</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>810.00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>18.79</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>854.08</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>TS-022</t>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>TS-044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0095928</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>568.00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>17.04</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>610.04</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>TS-023</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>TS-045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0095931</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>10.50</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>535.50</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>TS-024</t>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>TS-046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0095926</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>560.00</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>TS-024</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>TS-047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0095927</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>920.00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>27.76</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>46.00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>993.76</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>TS-024</t>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>TS-048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0095957</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>23.89</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>548.89</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>TS-025</t>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>TS-049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0095930</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>603.00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>18.84</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>646.84</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>TS-026</t>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>TS-050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0095933</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>25.90</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>540.90</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>TS-026</t>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>TS-051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0095936</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>25.20</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>25.46</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>550.66</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>TS-026</t>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>TS-052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0095938</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>732.00</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>30.28</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>787.28</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>TS-027</t>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>TS-053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0095934</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>625.00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>647.75</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>TS-028</t>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>TS-054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0095962</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>31.50</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>556.50</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>TS-028</t>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>TS-055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0095940</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>535.00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>26.75</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>586.75</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>TS-028</t>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>TS-056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0095937</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>15.75</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>540.75</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>TS-029</t>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>TS-057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0095942</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>11.81</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>536.99</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>TS-030</t>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>TS-058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0095966</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>779.00</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>23.37</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>827.37</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>TS-030</t>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>TS-059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0095941</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>10.50</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>535.50</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>TS-030</t>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>TS-060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0095954</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>560.00</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TS-031</t>
-        </is>
-      </c>
+      <c r="A62" s="3" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TS-032</t>
-        </is>
-      </c>
+      <c r="A63" s="3" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TS-032</t>
-        </is>
-      </c>
+      <c r="A64" s="3" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TS-032</t>
-        </is>
-      </c>
+      <c r="A65" s="3" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TS-033</t>
-        </is>
-      </c>
+      <c r="A66" s="3" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TS-034</t>
-        </is>
-      </c>
+      <c r="A67" s="3" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TS-034</t>
-        </is>
-      </c>
+      <c r="A68" s="3" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TS-034</t>
-        </is>
-      </c>
+      <c r="A69" s="3" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TS-035</t>
-        </is>
-      </c>
+      <c r="A70" s="3" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TS-036</t>
-        </is>
-      </c>
+      <c r="A71" s="3" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TS-036</t>
-        </is>
-      </c>
+      <c r="A72" s="3" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TS-036</t>
-        </is>
-      </c>
+      <c r="A73" s="3" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TS-037</t>
-        </is>
-      </c>
+      <c r="A74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>TS-038</t>
-        </is>
-      </c>
+      <c r="A75" s="3" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>TS-038</t>
-        </is>
-      </c>
+      <c r="A76" s="3" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>TS-038</t>
-        </is>
-      </c>
+      <c r="A77" s="3" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>TS-039</t>
-        </is>
-      </c>
+      <c r="A78" s="3" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>TS-040</t>
-        </is>
-      </c>
+      <c r="A79" s="3" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>TS-040</t>
-        </is>
-      </c>
+      <c r="A80" s="3" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>TS-040</t>
-        </is>
-      </c>
+      <c r="A81" s="3" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>TS-041</t>
-        </is>
-      </c>
+      <c r="A82" s="3" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>TS-042</t>
-        </is>
-      </c>
+      <c r="A83" s="3" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>TS-042</t>
-        </is>
-      </c>
+      <c r="A84" s="3" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>TS-042</t>
-        </is>
-      </c>
+      <c r="A85" s="3" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>TS-043</t>
-        </is>
-      </c>
+      <c r="A86" s="3" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>TS-044</t>
-        </is>
-      </c>
+      <c r="A87" s="3" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>TS-044</t>
-        </is>
-      </c>
+      <c r="A88" s="3" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>TS-044</t>
-        </is>
-      </c>
+      <c r="A89" s="3" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>TS-045</t>
-        </is>
-      </c>
+      <c r="A90" s="3" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>TS-046</t>
-        </is>
-      </c>
+      <c r="A91" s="3" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>TS-046</t>
-        </is>
-      </c>
+      <c r="A92" s="3" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>TS-046</t>
-        </is>
-      </c>
+      <c r="A93" s="3" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>TS-047</t>
-        </is>
-      </c>
+      <c r="A94" s="3" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>TS-048</t>
-        </is>
-      </c>
+      <c r="A95" s="3" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>TS-048</t>
-        </is>
-      </c>
+      <c r="A96" s="3" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>TS-048</t>
-        </is>
-      </c>
+      <c r="A97" s="3" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>TS-049</t>
-        </is>
-      </c>
+      <c r="A98" s="3" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>TS-050</t>
-        </is>
-      </c>
+      <c r="A99" s="3" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>TS-050</t>
-        </is>
-      </c>
+      <c r="A100" s="3" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>TS-050</t>
-        </is>
-      </c>
+      <c r="A101" s="3" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>TS-051</t>
-        </is>
-      </c>
+      <c r="A102" s="3" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>TS-052</t>
-        </is>
-      </c>
+      <c r="A103" s="3" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>TS-052</t>
-        </is>
-      </c>
+      <c r="A104" s="3" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>TS-052</t>
-        </is>
-      </c>
+      <c r="A105" s="3" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>TS-053</t>
-        </is>
-      </c>
+      <c r="A106" s="3" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>TS-054</t>
-        </is>
-      </c>
+      <c r="A107" s="3" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>TS-054</t>
-        </is>
-      </c>
+      <c r="A108" s="3" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>TS-054</t>
-        </is>
-      </c>
+      <c r="A109" s="3" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>TS-055</t>
-        </is>
-      </c>
+      <c r="A110" s="3" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>TS-056</t>
-        </is>
-      </c>
+      <c r="A111" s="3" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>TS-056</t>
-        </is>
-      </c>
+      <c r="A112" s="3" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>TS-056</t>
-        </is>
-      </c>
+      <c r="A113" s="3" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>TS-057</t>
-        </is>
-      </c>
+      <c r="A114" s="3" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>TS-058</t>
-        </is>
-      </c>
+      <c r="A115" s="3" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>TS-058</t>
-        </is>
-      </c>
+      <c r="A116" s="3" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>TS-058</t>
-        </is>
-      </c>
+      <c r="A117" s="3" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>TS-059</t>
-        </is>
-      </c>
+      <c r="A118" s="3" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>TS-060</t>
-        </is>
-      </c>
+      <c r="A119" s="3" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>TS-060</t>
-        </is>
-      </c>
+      <c r="A120" s="3" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>TS-060</t>
-        </is>
-      </c>
+      <c r="A121" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
